--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -93,7 +93,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">P506528</t>
+    <t xml:space="preserve">P511539</t>
   </si>
   <si>
     <t xml:space="preserve">Human Capital Protection Project</t>
@@ -108,7 +108,25 @@
     <t xml:space="preserve">Ousmane Deme (ADM)</t>
   </si>
   <si>
-    <t xml:space="preserve">P511539</t>
+    <t xml:space="preserve">P174620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR- Public Sector Digital Governance Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Project Development objective (PDO) is: To (i) improve efficiency and transparency in key areas of public resources management, and (ii) lay foundations for a trusted and inclusive digital government.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central African Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P174620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amadou Makhtar Fall (ADM)</t>
   </si>
   <si>
     <t xml:space="preserve">P169405</t>
@@ -219,52 +237,37 @@
     <t xml:space="preserve">Raymond Muhula (ADM)</t>
   </si>
   <si>
-    <t xml:space="preserve">P513735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mali Emergency Access to Essential Services Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To maintain continued access to essential health and education services in Mali.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Mali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P513735</t>
+    <t xml:space="preserve">P174822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niger Public Sector Management for Resilience and Service Delivery Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The PDO is to strengthen public expenditure and human resources management to improve the availability in underserved areas of (i) textbooks, and essential medicines, and (ii) teachers, and health workers in public primary schools and health centers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Niger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P174822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murielle Babatounde (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P509601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niger Food Security and Emergency Access to Essential  Services Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To maintain continuous access to adequate food, essential healthcare, and education services to people of Niger and strengthen revenue mobilization for the delivery of these services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P509601</t>
   </si>
   <si>
     <t xml:space="preserve">Tahirou Kalam (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P174822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niger Public Sector Management for Resilience and Service Delivery Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The PDO is to strengthen public expenditure and human resources management to improve the availability in underserved areas of (i) textbooks, and essential medicines, and (ii) teachers, and health workers in public primary schools and health centers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Niger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P174822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murielle Babatounde (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P509601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niger Food Security and Emergency Access to Essential  Services Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To maintain continuous access to adequate food, essential healthcare, and education services to people of Niger and strengthen revenue mobilization for the delivery of these services.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P509601</t>
   </si>
   <si>
     <t xml:space="preserve">P510613</t>
@@ -843,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>28</v>
@@ -873,20 +876,22 @@
         <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>20</v>
@@ -895,40 +900,42 @@
         <v>29</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="M4" s="1" t="n">
+        <v>35000000</v>
+      </c>
       <c r="N4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2020</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>20</v>
@@ -940,7 +947,7 @@
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>24</v>
@@ -954,25 +961,25 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2024</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>20</v>
@@ -984,10 +991,10 @@
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>500000000</v>
@@ -998,25 +1005,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>20</v>
@@ -1028,7 +1035,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>24</v>
@@ -1042,25 +1049,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>20</v>
@@ -1072,7 +1079,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>24</v>
@@ -1086,25 +1093,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>20</v>
@@ -1116,7 +1123,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>24</v>
@@ -1128,25 +1135,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>20</v>
@@ -1158,7 +1165,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>24</v>
@@ -1170,25 +1177,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>20</v>
@@ -1200,7 +1207,7 @@
         <v>22</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>24</v>
@@ -1214,55 +1221,57 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1" t="n">
+        <v>191500000</v>
+      </c>
       <c r="N12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
@@ -1271,66 +1280,64 @@
         <v>77</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>191500000</v>
-      </c>
+      <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>24</v>
@@ -1342,131 +1349,89 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="n">
+        <v>40000000</v>
+      </c>
       <c r="N15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>40000000</v>
+        <v>65000000</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="N17" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1543,35 +1508,35 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1581,33 +1546,33 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1617,35 +1582,35 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1655,35 +1620,35 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2026</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1693,33 +1658,33 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -93,34 +93,22 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">P511539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Capital Protection Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P506528</t>
+    <t xml:space="preserve">P174620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR- Public Sector Digital Governance Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Project Development objective (PDO) is: To (i) improve efficiency and transparency in key areas of public resources management, and (ii) lay foundations for a trusted and inclusive digital government.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central African Republic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P174620</t>
   </si>
   <si>
     <t xml:space="preserve">IPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ousmane Deme (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P174620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAR- Public Sector Digital Governance Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Project Development objective (PDO) is: To (i) improve efficiency and transparency in key areas of public resources management, and (ii) lay foundations for a trusted and inclusive digital government.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central African Republic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P174620</t>
   </si>
   <si>
     <t xml:space="preserve">DDT</t>
@@ -838,78 +826,82 @@
       <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="1"/>
+      <c r="M3" s="1" t="n">
+        <v>35000000</v>
+      </c>
       <c r="N3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>35000000</v>
+        <v>80000000</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>25</v>
@@ -917,43 +909,43 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>80000000</v>
+        <v>500000000</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>25</v>
@@ -961,43 +953,43 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>500000000</v>
+        <v>80000000</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>25</v>
@@ -1005,43 +997,43 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>80000000</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>25</v>
@@ -1049,25 +1041,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>20</v>
@@ -1079,39 +1071,37 @@
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>20</v>
@@ -1123,7 +1113,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>24</v>
@@ -1135,25 +1125,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>20</v>
@@ -1165,37 +1155,39 @@
         <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1" t="n">
+        <v>150000000</v>
+      </c>
       <c r="N10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>20</v>
@@ -1207,13 +1199,13 @@
         <v>22</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>150000000</v>
+        <v>191500000</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>25</v>
@@ -1221,81 +1213,79 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>191500000</v>
-      </c>
+      <c r="M12" s="1"/>
       <c r="N12" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>24</v>
@@ -1307,131 +1297,89 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1" t="n">
+        <v>40000000</v>
+      </c>
       <c r="N14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>40000000</v>
+        <v>65000000</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>65000000</v>
-      </c>
-      <c r="N16" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1508,35 +1456,35 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1546,33 +1494,33 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1582,35 +1530,35 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1620,35 +1568,35 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2026</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1658,33 +1606,33 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t xml:space="preserve">commitment_amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_pfm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_procurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_public_admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theme_env_social</t>
   </si>
   <si>
     <t xml:space="preserve">comments</t>
@@ -728,7 +740,11 @@
     <col min="11" max="11" width="26.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,613 +790,785 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2023</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>150000000</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
+      <c r="N2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>35000000</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2020</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>80000000</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2024</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>500000000</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>25</v>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1" t="n">
         <v>80000000</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>25</v>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
-        <v>25</v>
+      <c r="N8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
-        <v>25</v>
+      <c r="N9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>150000000</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>25</v>
+      <c r="N10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>2022</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>191500000</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>25</v>
+      <c r="N11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M12" s="1"/>
-      <c r="N12" s="1" t="s">
-        <v>25</v>
+      <c r="N12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>2025</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M13" s="1"/>
-      <c r="N13" s="1" t="s">
-        <v>25</v>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>2021</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>40000000</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>25</v>
+      <c r="N14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>2024</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>65000000</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>25</v>
+      <c r="N15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1407,7 +1595,11 @@
     <col min="11" max="11" width="33.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="14.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="17.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="16.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,191 +1645,263 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>2012</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
+      <c r="N2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
+      <c r="N3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2026</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1" t="s">
-        <v>25</v>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2027</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -72,6 +72,9 @@
     <t xml:space="preserve">theme_env_social</t>
   </si>
   <si>
+    <t xml:space="preserve">ida_cycle_approval</t>
+  </si>
+  <si>
     <t xml:space="preserve">comments</t>
   </si>
   <si>
@@ -108,6 +111,9 @@
     <t xml:space="preserve">IDA</t>
   </si>
   <si>
+    <t xml:space="preserve">Pre-IDA21</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
@@ -394,6 +400,9 @@
   </si>
   <si>
     <t xml:space="preserve">Suren Chandra Tripathi (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDA21</t>
   </si>
   <si>
     <t xml:space="preserve">P501226</t>
@@ -761,7 +770,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -825,22 +835,25 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2023</v>
@@ -848,22 +861,22 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>150000000</v>
@@ -881,24 +894,27 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2022</v>
@@ -906,22 +922,22 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>35000000</v>
@@ -931,24 +947,27 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2020</v>
@@ -956,22 +975,22 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>80000000</v>
@@ -989,24 +1008,27 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2024</v>
@@ -1014,22 +1036,22 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>500000000</v>
@@ -1047,24 +1069,27 @@
         <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2025</v>
@@ -1072,22 +1097,22 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>80000000</v>
@@ -1105,24 +1130,27 @@
         <v>1</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2025</v>
@@ -1130,22 +1158,22 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0</v>
@@ -1163,24 +1191,27 @@
         <v>1</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2025</v>
@@ -1188,22 +1219,22 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="n">
@@ -1219,24 +1250,27 @@
         <v>1</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2025</v>
@@ -1244,22 +1278,22 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2" t="n">
@@ -1275,24 +1309,27 @@
         <v>1</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2022</v>
@@ -1300,22 +1337,22 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>150000000</v>
@@ -1333,24 +1370,27 @@
         <v>1</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>2022</v>
@@ -1358,22 +1398,22 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>191500000</v>
@@ -1391,24 +1431,27 @@
         <v>1</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>2025</v>
@@ -1416,22 +1459,22 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="n">
@@ -1447,24 +1490,27 @@
         <v>1</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>2025</v>
@@ -1472,22 +1518,22 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="n">
@@ -1503,24 +1549,27 @@
         <v>1</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>2021</v>
@@ -1528,22 +1577,22 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>40000000</v>
@@ -1561,24 +1610,27 @@
         <v>1</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>2024</v>
@@ -1586,22 +1638,22 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>65000000</v>
@@ -1619,7 +1671,10 @@
         <v>1</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1652,7 +1707,8 @@
     <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
     <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
     <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="8.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,22 +1772,25 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2012</v>
@@ -1739,17 +1798,17 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1766,42 +1825,47 @@
         <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2027</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="n">
+        <v>45210</v>
+      </c>
       <c r="H3" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1818,44 +1882,49 @@
         <v>0</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2027</v>
       </c>
-      <c r="G4" s="2"/>
+      <c r="G4" s="2" t="n">
+        <v>45831</v>
+      </c>
       <c r="H4" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1872,24 +1941,27 @@
         <v>0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2026</v>
@@ -1898,20 +1970,20 @@
         <v>46087</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1928,42 +2000,47 @@
         <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>31</v>
+        <v>129</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2027</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="2" t="n">
+        <v>45261</v>
+      </c>
       <c r="H6" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1980,7 +2057,10 @@
         <v>0</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">proj_approval_fy</t>
   </si>
   <si>
-    <t xml:space="preserve">asa_cn_approval_date</t>
+    <t xml:space="preserve">asa_approval_date</t>
   </si>
   <si>
     <t xml:space="preserve">task_type</t>
@@ -333,39 +333,27 @@
     <t xml:space="preserve">Ibrahim El ghandour (ADM)</t>
   </si>
   <si>
-    <t xml:space="preserve">P129447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NG Donor Coordination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Series of meetings and discussions with other active donors in Nigeria, in support of donor coordination.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P129447</t>
+    <t xml:space="preserve">P500428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nigeria Transparent, Effective and Accountable Public Institutions (TEA) PASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advisory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P500428</t>
   </si>
   <si>
     <t xml:space="preserve">Analytic and Advisory Activities Product</t>
   </si>
   <si>
-    <t xml:space="preserve">Marie Francoise Marie-Nelly (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P500428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nigeria Transparent, Effective and Accountable Public Institutions (TEA) PASA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advisory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P500428</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deborah Hannah Isser (ADM)</t>
   </si>
   <si>
+    <t xml:space="preserve">IDA21</t>
+  </si>
+  <si>
     <t xml:space="preserve">P510239</t>
   </si>
   <si>
@@ -400,9 +388,6 @@
   </si>
   <si>
     <t xml:space="preserve">Suren Chandra Tripathi (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDA21</t>
   </si>
   <si>
     <t xml:space="preserve">P501226</t>
@@ -757,7 +742,7 @@
     <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="30.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
@@ -1694,13 +1679,13 @@
     <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="33.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="28.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
@@ -1783,9 +1768,7 @@
       <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>108</v>
-      </c>
+      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
@@ -1793,10 +1776,14 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2012</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+        <v>2027</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>45210</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>109</v>
       </c>
@@ -1819,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>33</v>
@@ -1833,29 +1820,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2027</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45210</v>
+        <v>45831</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>110</v>
@@ -1865,12 +1854,12 @@
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
@@ -1882,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>33</v>
@@ -1890,31 +1879,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45831</v>
+        <v>46087</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>110</v>
@@ -1924,7 +1913,7 @@
         <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1938,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>33</v>
@@ -1949,28 +1938,26 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46087</v>
+        <v>45261</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>127</v>
@@ -1983,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1997,69 +1984,12 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>45261</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -351,43 +351,58 @@
     <t xml:space="preserve">Deborah Hannah Isser (ADM)</t>
   </si>
   <si>
+    <t xml:space="preserve">P129447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NG Donor Coordination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Series of meetings and discussions with other active donors in Nigeria, in support of donor coordination.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P129447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marie Francoise Marie-Nelly (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P510239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building  the Capacity of Parliamentarians for Economic and Financial Governance in Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To improve the capacity of Ghana?s Parliament to drive fiscally sustainable growth through the effective, transparent and accountable management of public finances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P510239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smile Kwawukume (ADM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P513657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sovereign Wealth Fund Options to Support Macro-Fiscal Stability and Sustainable Development in Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To support the Government of Guinea (GoG) to design the macro-fiscal and operational aspects of its Sovereign Fund, including assessing and designing appropriate savings, stabilization, and investment mechanisms, all anchored in Guinea's macro?fiscal framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Republic of Guinea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opswork.worldbank.org/home/P513657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suren Chandra Tripathi (ADM)</t>
+  </si>
+  <si>
     <t xml:space="preserve">IDA21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P510239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building  the Capacity of Parliamentarians for Economic and Financial Governance in Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To improve the capacity of Ghana?s Parliament to drive fiscally sustainable growth through the effective, transparent and accountable management of public finances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P510239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smile Kwawukume (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P513657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sovereign Wealth Fund Options to Support Macro-Fiscal Stability and Sustainable Development in Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To support the Government of Guinea (GoG) to design the macro-fiscal and operational aspects of its Sovereign Fund, including assessing and designing appropriate savings, stabilization, and investment mechanisms, all anchored in Guinea's macro?fiscal framework.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Republic of Guinea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P513657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suren Chandra Tripathi (ADM)</t>
   </si>
   <si>
     <t xml:space="preserve">P501226</t>
@@ -1685,7 +1700,7 @@
     <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="28.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="33.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
@@ -1776,7 +1791,7 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>45210</v>
@@ -1812,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>33</v>
@@ -1820,31 +1835,25 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>45831</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>110</v>
@@ -1854,56 +1863,54 @@
         <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46087</v>
+        <v>45831</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>110</v>
@@ -1913,7 +1920,7 @@
         <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1927,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>33</v>
@@ -1938,26 +1945,28 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>45261</v>
+        <v>46087</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>127</v>
@@ -1970,7 +1979,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1984,12 +1993,69 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="U5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>45261</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -349,21 +349,6 @@
   </si>
   <si>
     <t xml:space="preserve">Deborah Hannah Isser (ADM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P129447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NG Donor Coordination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Series of meetings and discussions with other active donors in Nigeria, in support of donor coordination.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opswork.worldbank.org/home/P129447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marie Francoise Marie-Nelly (ADM)</t>
   </si>
   <si>
     <t xml:space="preserve">P510239</t>
@@ -1700,7 +1685,7 @@
     <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="33.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="28.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
     <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
@@ -1847,11 +1832,17 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45831</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="I3" s="2" t="s">
         <v>115</v>
       </c>
@@ -1868,18 +1859,20 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="2"/>
+      <c r="T3" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="U3" s="2" t="s">
         <v>33</v>
       </c>
@@ -1898,19 +1891,19 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45831</v>
+        <v>46087</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>110</v>
@@ -1920,7 +1913,7 @@
         <v>29</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1934,10 +1927,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>33</v>
@@ -1945,28 +1938,26 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46087</v>
+        <v>45261</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>127</v>
@@ -1979,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1993,69 +1984,12 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>45261</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/extdata/wb_projects_gov_afw.xlsx
+++ b/inst/extdata/wb_projects_gov_afw.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -27,6 +27,9 @@
     <t xml:space="preserve">region</t>
   </si>
   <si>
+    <t xml:space="preserve">country_code</t>
+  </si>
+  <si>
     <t xml:space="preserve">country_name</t>
   </si>
   <si>
@@ -90,6 +93,9 @@
     <t xml:space="preserve">Western and Central Africa</t>
   </si>
   <si>
+    <t xml:space="preserve">BFA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Burkina Faso</t>
   </si>
   <si>
@@ -126,6 +132,9 @@
     <t xml:space="preserve">The Project Development objective (PDO) is: To (i) improve efficiency and transparency in key areas of public resources management, and (ii) lay foundations for a trusted and inclusive digital government.</t>
   </si>
   <si>
+    <t xml:space="preserve">CAF</t>
+  </si>
+  <si>
     <t xml:space="preserve">Central African Republic</t>
   </si>
   <si>
@@ -150,6 +159,9 @@
     <t xml:space="preserve">The project development objective is to develop sustainable capacity in managing procurement, environment and social standards in the public and private sectors.</t>
   </si>
   <si>
+    <t xml:space="preserve">NGA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Federal Republic of Nigeria</t>
   </si>
   <si>
@@ -204,6 +216,9 @@
     <t xml:space="preserve">Improve public financial management systems and accountability for enhanced efficiency of social spending</t>
   </si>
   <si>
+    <t xml:space="preserve">MRT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Islamic Republic of Mauritania</t>
   </si>
   <si>
@@ -222,6 +237,9 @@
     <t xml:space="preserve">To improve domestic revenue mobilization; and the accountability and transparency of public finances, including in selected sectors.</t>
   </si>
   <si>
+    <t xml:space="preserve">CMR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Cameroon</t>
   </si>
   <si>
@@ -240,6 +258,9 @@
     <t xml:space="preserve">To improve resource mobilization and allocation, budget execution and accountability.</t>
   </si>
   <si>
+    <t xml:space="preserve">GHA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Ghana</t>
   </si>
   <si>
@@ -258,6 +279,9 @@
     <t xml:space="preserve">The PDO is to strengthen public expenditure and human resources management to improve the availability in underserved areas of (i) textbooks, and essential medicines, and (ii) teachers, and health workers in public primary schools and health centers.</t>
   </si>
   <si>
+    <t xml:space="preserve">NER</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Niger</t>
   </si>
   <si>
@@ -291,6 +315,9 @@
     <t xml:space="preserve">To improve public debt sustainability, strengthen public financial management, and increase domestic resource mobilization.</t>
   </si>
   <si>
+    <t xml:space="preserve">SEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Senegal</t>
   </si>
   <si>
@@ -309,6 +336,9 @@
     <t xml:space="preserve">The PDO is to improve resource management, transparency and accountability of government systems for enabling the delivery of local development projects and basic services.</t>
   </si>
   <si>
+    <t xml:space="preserve">SLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Sierra Leone</t>
   </si>
   <si>
@@ -324,6 +354,9 @@
     <t xml:space="preserve">The PforR development objective is to enhance human resource and public expenditure management.</t>
   </si>
   <si>
+    <t xml:space="preserve">TGO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Republic of Togo</t>
   </si>
   <si>
@@ -373,6 +406,9 @@
   </si>
   <si>
     <t xml:space="preserve">To support the Government of Guinea (GoG) to design the macro-fiscal and operational aspects of its Sovereign Fund, including assessing and designing appropriate savings, stabilization, and investment mechanisms, all anchored in Guinea's macro?fiscal framework.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIN</t>
   </si>
   <si>
     <t xml:space="preserve">Republic of Guinea</t>
@@ -740,23 +776,24 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="30.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="26.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="17.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="26.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,843 +860,888 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>150000000</v>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>35000000</v>
       </c>
-      <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="2" t="n">
         <v>80000000</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>32</v>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>500000000</v>
       </c>
-      <c r="P5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
+      <c r="T5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" s="2" t="n">
         <v>80000000</v>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="2"/>
       <c r="Q8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="2"/>
       <c r="Q9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>150000000</v>
       </c>
-      <c r="P10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>32</v>
+      <c r="T10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="2" t="n">
         <v>191500000</v>
       </c>
-      <c r="P11" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="2"/>
       <c r="Q12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" s="2"/>
       <c r="Q13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
-        <v>99</v>
-      </c>
+      <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O14" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" s="2" t="n">
         <v>40000000</v>
       </c>
-      <c r="P14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>32</v>
+      <c r="T14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F15" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O15" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>65000000</v>
       </c>
-      <c r="P15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>32</v>
+      <c r="T15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1677,23 +1759,24 @@
     <col min="2" max="2" width="40.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="26.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="42.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="40.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="7.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="28.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="17.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="17.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="16.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="18.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="27.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="42.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="40.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="7.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="28.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="17.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="17.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="18.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="16.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="18.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="8.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1760,48 +1843,51 @@
       <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>45210</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="N2" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="O2" s="2"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="2"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
@@ -1811,58 +1897,61 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
+      <c r="T2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>45831</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="O3" s="2"/>
-      <c r="P3" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P3" s="2"/>
       <c r="Q3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
@@ -1870,115 +1959,121 @@
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>32</v>
+      <c r="T3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="O4" s="2"/>
-      <c r="P4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P4" s="2"/>
       <c r="Q4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>124</v>
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>33</v>
+        <v>136</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="O5" s="2"/>
-      <c r="P5" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" s="2"/>
       <c r="Q5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0</v>
@@ -1986,11 +2081,14 @@
       <c r="S5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
